--- a/servers/maze_main_server/conf.d/data/maze_reborn_cost_v8【迷宫-复活消耗】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_reborn_cost_v8【迷宫-复活消耗】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD80D37-2F0C-4ACA-BFB0-F9DBF7861123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07FF846-99B8-44EC-9D45-F1CCB91592F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,15 +82,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46200001:5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46200001:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46200001:50</t>
+    <t>46900001:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900001:1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900001:5000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_reborn_cost_v8【迷宫-复活消耗】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_reborn_cost_v8【迷宫-复活消耗】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07FF846-99B8-44EC-9D45-F1CCB91592F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC54964-E9B1-4433-AFD8-502D1BC3973A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_reborn_cost_v8" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -82,15 +80,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46900001:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46900001:1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46900001:5000</t>
+    <t>46200001:5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
